--- a/pregenereated_results/s2/ate_summary_survey.xlsx
+++ b/pregenereated_results/s2/ate_summary_survey.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4005965890818798</v>
+        <v>0.3982233096578141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03981363902264499</v>
+        <v>0.03926983810596111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3225632905040172</v>
+        <v>0.3212558412914117</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4786298876597425</v>
+        <v>0.4751907780242164</v>
       </c>
       <c r="G2" t="n">
-        <v>8.150040732680005e-24</v>
+        <v>3.645104327879786e-24</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4788625826755514</v>
+        <v>0.4740212656916218</v>
       </c>
       <c r="I2" t="n">
-        <v>11.97054240323347</v>
+        <v>11.8520500782549</v>
       </c>
       <c r="J2" t="n">
-        <v>3.787283134131842</v>
+        <v>3.783304057116402</v>
       </c>
       <c r="K2" t="n">
-        <v>3.382392415759588</v>
+        <v>3.382418162625982</v>
       </c>
       <c r="L2" t="n">
         <v>7220</v>
       </c>
       <c r="M2" t="n">
-        <v>7099.15044992504</v>
+        <v>7094.386718944054</v>
       </c>
       <c r="N2" t="n">
-        <v>2.445012219804002e-23</v>
+        <v>1.093531298363936e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0408092366185924</v>
+        <v>-0.04059280522771685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04202937973037035</v>
+        <v>0.04219295914182773</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.123185307182676</v>
+        <v>-0.1232894855468692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04156683394549125</v>
+        <v>0.04210387509143552</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3315635759904207</v>
+        <v>0.3360117637295977</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05928839378035856</v>
+        <v>-0.06073443341649937</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.732908818643073</v>
+        <v>-1.775147039486122</v>
       </c>
       <c r="J3" t="n">
-        <v>3.136135279852918</v>
+        <v>3.134720965027061</v>
       </c>
       <c r="K3" t="n">
-        <v>3.19144002549645</v>
+        <v>3.191372519831829</v>
       </c>
       <c r="L3" t="n">
         <v>7220</v>
       </c>
       <c r="M3" t="n">
-        <v>7099.15044992504</v>
+        <v>7094.386718944054</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3315635759904207</v>
+        <v>0.3360117637295977</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2311650223435082</v>
+        <v>0.2300267851900341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,37 +648,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04307563847579732</v>
+        <v>0.04275687264023308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1467383223198777</v>
+        <v>0.1462248547236112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3155917223671388</v>
+        <v>0.3138287156564569</v>
       </c>
       <c r="G4" t="n">
-        <v>8.028324442825778e-08</v>
+        <v>7.453607464503556e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2684021523915693</v>
+        <v>0.2684816016281898</v>
       </c>
       <c r="I4" t="n">
-        <v>9.111190615044219</v>
+        <v>9.10917724022616</v>
       </c>
       <c r="J4" t="n">
-        <v>3.052338555404936</v>
+        <v>3.052316367566833</v>
       </c>
       <c r="K4" t="n">
-        <v>2.797456922795305</v>
+        <v>2.797488208390147</v>
       </c>
       <c r="L4" t="n">
         <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>7099.15044992504</v>
+        <v>7094.386718944054</v>
       </c>
       <c r="N4" t="n">
-        <v>1.204248666423867e-07</v>
+        <v>1.118041119675534e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
